--- a/artfynd/A 40662-2023 artfynd.xlsx
+++ b/artfynd/A 40662-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40662-2023 artfynd.xlsx
+++ b/artfynd/A 40662-2023 artfynd.xlsx
@@ -675,49 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109591255</v>
+        <v>109590546</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -729,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612402.2793752415</v>
+        <v>612359</v>
       </c>
       <c r="R2" t="n">
-        <v>6656710.587014053</v>
+        <v>6656777</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,40 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109590546</v>
+        <v>109590634</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -846,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612359.1726788243</v>
+        <v>612376</v>
       </c>
       <c r="R3" t="n">
-        <v>6656777.276972219</v>
+        <v>6656763</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109590634</v>
+        <v>109591255</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -972,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612376.6285439119</v>
+        <v>612402</v>
       </c>
       <c r="R4" t="n">
-        <v>6656763.308499195</v>
+        <v>6656711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40662-2023 artfynd.xlsx
+++ b/artfynd/A 40662-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109590546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109590634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109591255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>